--- a/data/US_5y_dens.xlsx
+++ b/data/US_5y_dens.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4140" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="4203" uniqueCount="203">
   <si>
     <t>date</t>
   </si>
@@ -609,6 +609,15 @@
     <t>2026-02-12</t>
   </si>
   <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-04-09</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
     <t>support</t>
   </si>
   <si>
@@ -658,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4138"/>
+  <dimension ref="A1:C4201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2">
@@ -46137,6 +46146,699 @@
         <v>0.014941508980672813</v>
       </c>
     </row>
+    <row r="4139">
+      <c r="A4139" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4139" s="1">
+        <v>-0.029999999999999999</v>
+      </c>
+      <c r="C4139" s="1">
+        <v>0.00013872600814565406</v>
+      </c>
+    </row>
+    <row r="4140">
+      <c r="A4140" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4140" s="1">
+        <v>-0.024999999999999998</v>
+      </c>
+      <c r="C4140" s="1">
+        <v>0.00011371209483085954</v>
+      </c>
+    </row>
+    <row r="4141">
+      <c r="A4141" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4141" s="1">
+        <v>-0.019999999999999997</v>
+      </c>
+      <c r="C4141" s="1">
+        <v>0.00021931910633004898</v>
+      </c>
+    </row>
+    <row r="4142">
+      <c r="A4142" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4142" s="1">
+        <v>-0.014999999999999999</v>
+      </c>
+      <c r="C4142" s="1">
+        <v>0.00044142028545971775</v>
+      </c>
+    </row>
+    <row r="4143">
+      <c r="A4143" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4143" s="1">
+        <v>-0.0099999999999999985</v>
+      </c>
+      <c r="C4143" s="1">
+        <v>0.00093874263496064125</v>
+      </c>
+    </row>
+    <row r="4144">
+      <c r="A4144" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4144" s="1">
+        <v>-0.0049999999999999975</v>
+      </c>
+      <c r="C4144" s="1">
+        <v>0.0021788307133053888</v>
+      </c>
+    </row>
+    <row r="4145">
+      <c r="A4145" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4145" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4145" s="1">
+        <v>0.0054871482600072638</v>
+      </c>
+    </row>
+    <row r="4146">
+      <c r="A4146" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4146" s="1">
+        <v>0.0050000000000000044</v>
+      </c>
+      <c r="C4146" s="1">
+        <v>0.014962713554322882</v>
+      </c>
+    </row>
+    <row r="4147">
+      <c r="A4147" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4147" s="1">
+        <v>0.010000000000000002</v>
+      </c>
+      <c r="C4147" s="1">
+        <v>0.042402054650534655</v>
+      </c>
+    </row>
+    <row r="4148">
+      <c r="A4148" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4148" s="1">
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="C4148" s="1">
+        <v>0.10874560716874836</v>
+      </c>
+    </row>
+    <row r="4149">
+      <c r="A4149" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4149" s="1">
+        <v>0.020000000000000004</v>
+      </c>
+      <c r="C4149" s="1">
+        <v>0.19695499951012987</v>
+      </c>
+    </row>
+    <row r="4150">
+      <c r="A4150" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4150" s="1">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="C4150" s="1">
+        <v>0.21542293431466272</v>
+      </c>
+    </row>
+    <row r="4151">
+      <c r="A4151" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4151" s="1">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="C4151" s="1">
+        <v>0.15894444294515611</v>
+      </c>
+    </row>
+    <row r="4152">
+      <c r="A4152" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4152" s="1">
+        <v>0.035000000000000003</v>
+      </c>
+      <c r="C4152" s="1">
+        <v>0.097918814686120986</v>
+      </c>
+    </row>
+    <row r="4153">
+      <c r="A4153" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4153" s="1">
+        <v>0.040000000000000008</v>
+      </c>
+      <c r="C4153" s="1">
+        <v>0.057650052584974548</v>
+      </c>
+    </row>
+    <row r="4154">
+      <c r="A4154" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4154" s="1">
+        <v>0.044999999999999998</v>
+      </c>
+      <c r="C4154" s="1">
+        <v>0.034272419972291433</v>
+      </c>
+    </row>
+    <row r="4155">
+      <c r="A4155" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4155" s="1">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="C4155" s="1">
+        <v>0.020940990537279311</v>
+      </c>
+    </row>
+    <row r="4156">
+      <c r="A4156" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4156" s="1">
+        <v>0.055000000000000007</v>
+      </c>
+      <c r="C4156" s="1">
+        <v>0.013200688615688173</v>
+      </c>
+    </row>
+    <row r="4157">
+      <c r="A4157" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4157" s="1">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="C4157" s="1">
+        <v>0.0085761449123331491</v>
+      </c>
+    </row>
+    <row r="4158">
+      <c r="A4158" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4158" s="1">
+        <v>0.065000000000000002</v>
+      </c>
+      <c r="C4158" s="1">
+        <v>0.0057278547990845495</v>
+      </c>
+    </row>
+    <row r="4159">
+      <c r="A4159" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4159" s="1">
+        <v>0.070000000000000007</v>
+      </c>
+      <c r="C4159" s="1">
+        <v>0.014762382645633676</v>
+      </c>
+    </row>
+    <row r="4160">
+      <c r="A4160" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4160" s="1">
+        <v>-0.029999999999999999</v>
+      </c>
+      <c r="C4160" s="1">
+        <v>0.00020927837139420941</v>
+      </c>
+    </row>
+    <row r="4161">
+      <c r="A4161" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4161" s="1">
+        <v>-0.024999999999999998</v>
+      </c>
+      <c r="C4161" s="1">
+        <v>0.00014226667269303823</v>
+      </c>
+    </row>
+    <row r="4162">
+      <c r="A4162" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4162" s="1">
+        <v>-0.019999999999999997</v>
+      </c>
+      <c r="C4162" s="1">
+        <v>0.00025260874515954049</v>
+      </c>
+    </row>
+    <row r="4163">
+      <c r="A4163" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4163" s="1">
+        <v>-0.014999999999999999</v>
+      </c>
+      <c r="C4163" s="1">
+        <v>0.00046618124835859647</v>
+      </c>
+    </row>
+    <row r="4164">
+      <c r="A4164" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4164" s="1">
+        <v>-0.0099999999999999985</v>
+      </c>
+      <c r="C4164" s="1">
+        <v>0.00090505205682668837</v>
+      </c>
+    </row>
+    <row r="4165">
+      <c r="A4165" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4165" s="1">
+        <v>-0.0049999999999999975</v>
+      </c>
+      <c r="C4165" s="1">
+        <v>0.0019170478000866747</v>
+      </c>
+    </row>
+    <row r="4166">
+      <c r="A4166" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4166" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4166" s="1">
+        <v>0.004410546312143015</v>
+      </c>
+    </row>
+    <row r="4167">
+      <c r="A4167" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4167" s="1">
+        <v>0.0050000000000000044</v>
+      </c>
+      <c r="C4167" s="1">
+        <v>0.01113581806964559</v>
+      </c>
+    </row>
+    <row r="4168">
+      <c r="A4168" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4168" s="1">
+        <v>0.010000000000000002</v>
+      </c>
+      <c r="C4168" s="1">
+        <v>0.030535860773150993</v>
+      </c>
+    </row>
+    <row r="4169">
+      <c r="A4169" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4169" s="1">
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="C4169" s="1">
+        <v>0.083453769990375182</v>
+      </c>
+    </row>
+    <row r="4170">
+      <c r="A4170" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4170" s="1">
+        <v>0.020000000000000004</v>
+      </c>
+      <c r="C4170" s="1">
+        <v>0.17864524460368106</v>
+      </c>
+    </row>
+    <row r="4171">
+      <c r="A4171" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4171" s="1">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="C4171" s="1">
+        <v>0.22793706874000674</v>
+      </c>
+    </row>
+    <row r="4172">
+      <c r="A4172" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4172" s="1">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="C4172" s="1">
+        <v>0.17766534849821988</v>
+      </c>
+    </row>
+    <row r="4173">
+      <c r="A4173" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4173" s="1">
+        <v>0.035000000000000003</v>
+      </c>
+      <c r="C4173" s="1">
+        <v>0.10898892419313516</v>
+      </c>
+    </row>
+    <row r="4174">
+      <c r="A4174" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4174" s="1">
+        <v>0.040000000000000008</v>
+      </c>
+      <c r="C4174" s="1">
+        <v>0.063360971451735318</v>
+      </c>
+    </row>
+    <row r="4175">
+      <c r="A4175" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4175" s="1">
+        <v>0.044999999999999998</v>
+      </c>
+      <c r="C4175" s="1">
+        <v>0.037480263184730044</v>
+      </c>
+    </row>
+    <row r="4176">
+      <c r="A4176" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4176" s="1">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="C4176" s="1">
+        <v>0.022986661198995149</v>
+      </c>
+    </row>
+    <row r="4177">
+      <c r="A4177" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4177" s="1">
+        <v>0.055000000000000007</v>
+      </c>
+      <c r="C4177" s="1">
+        <v>0.014641372776644217</v>
+      </c>
+    </row>
+    <row r="4178">
+      <c r="A4178" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4178" s="1">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="C4178" s="1">
+        <v>0.0096555444956677085</v>
+      </c>
+    </row>
+    <row r="4179">
+      <c r="A4179" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4179" s="1">
+        <v>0.065000000000000002</v>
+      </c>
+      <c r="C4179" s="1">
+        <v>0.0065660416455161508</v>
+      </c>
+    </row>
+    <row r="4180">
+      <c r="A4180" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4180" s="1">
+        <v>0.070000000000000007</v>
+      </c>
+      <c r="C4180" s="1">
+        <v>0.018644129171835</v>
+      </c>
+    </row>
+    <row r="4181">
+      <c r="A4181" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4181" s="1">
+        <v>-0.029999999999999999</v>
+      </c>
+      <c r="C4181" s="1">
+        <v>0.00036962425892991363</v>
+      </c>
+    </row>
+    <row r="4182">
+      <c r="A4182" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4182" s="1">
+        <v>-0.024999999999999998</v>
+      </c>
+      <c r="C4182" s="1">
+        <v>0.00022848504858094865</v>
+      </c>
+    </row>
+    <row r="4183">
+      <c r="A4183" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4183" s="1">
+        <v>-0.019999999999999997</v>
+      </c>
+      <c r="C4183" s="1">
+        <v>0.00038997905646173252</v>
+      </c>
+    </row>
+    <row r="4184">
+      <c r="A4184" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4184" s="1">
+        <v>-0.014999999999999999</v>
+      </c>
+      <c r="C4184" s="1">
+        <v>0.0006893756189975701</v>
+      </c>
+    </row>
+    <row r="4185">
+      <c r="A4185" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4185" s="1">
+        <v>-0.0099999999999999985</v>
+      </c>
+      <c r="C4185" s="1">
+        <v>0.0012750026321238736</v>
+      </c>
+    </row>
+    <row r="4186">
+      <c r="A4186" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4186" s="1">
+        <v>-0.0049999999999999975</v>
+      </c>
+      <c r="C4186" s="1">
+        <v>0.0025419760996005986</v>
+      </c>
+    </row>
+    <row r="4187">
+      <c r="A4187" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4187" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4187" s="1">
+        <v>0.0054223826546351559</v>
+      </c>
+    </row>
+    <row r="4188">
+      <c r="A4188" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4188" s="1">
+        <v>0.0050000000000000044</v>
+      </c>
+      <c r="C4188" s="1">
+        <v>0.012428114491530121</v>
+      </c>
+    </row>
+    <row r="4189">
+      <c r="A4189" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4189" s="1">
+        <v>0.010000000000000002</v>
+      </c>
+      <c r="C4189" s="1">
+        <v>0.030169497878979816</v>
+      </c>
+    </row>
+    <row r="4190">
+      <c r="A4190" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4190" s="1">
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="C4190" s="1">
+        <v>0.072399436475404463</v>
+      </c>
+    </row>
+    <row r="4191">
+      <c r="A4191" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4191" s="1">
+        <v>0.020000000000000004</v>
+      </c>
+      <c r="C4191" s="1">
+        <v>0.14501397789865825</v>
+      </c>
+    </row>
+    <row r="4192">
+      <c r="A4192" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4192" s="1">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="C4192" s="1">
+        <v>0.19746904478770513</v>
+      </c>
+    </row>
+    <row r="4193">
+      <c r="A4193" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4193" s="1">
+        <v>0.029999999999999999</v>
+      </c>
+      <c r="C4193" s="1">
+        <v>0.1770636268399694</v>
+      </c>
+    </row>
+    <row r="4194">
+      <c r="A4194" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4194" s="1">
+        <v>0.035000000000000003</v>
+      </c>
+      <c r="C4194" s="1">
+        <v>0.12288231429011462</v>
+      </c>
+    </row>
+    <row r="4195">
+      <c r="A4195" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4195" s="1">
+        <v>0.040000000000000008</v>
+      </c>
+      <c r="C4195" s="1">
+        <v>0.077763141646372255</v>
+      </c>
+    </row>
+    <row r="4196">
+      <c r="A4196" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4196" s="1">
+        <v>0.044999999999999998</v>
+      </c>
+      <c r="C4196" s="1">
+        <v>0.048749988778994002</v>
+      </c>
+    </row>
+    <row r="4197">
+      <c r="A4197" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4197" s="1">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="C4197" s="1">
+        <v>0.031196622806758036</v>
+      </c>
+    </row>
+    <row r="4198">
+      <c r="A4198" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4198" s="1">
+        <v>0.055000000000000007</v>
+      </c>
+      <c r="C4198" s="1">
+        <v>0.020544011989927499</v>
+      </c>
+    </row>
+    <row r="4199">
+      <c r="A4199" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4199" s="1">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="C4199" s="1">
+        <v>0.013926640560378239</v>
+      </c>
+    </row>
+    <row r="4200">
+      <c r="A4200" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4200" s="1">
+        <v>0.065000000000000002</v>
+      </c>
+      <c r="C4200" s="1">
+        <v>0.0096973519675439008</v>
+      </c>
+    </row>
+    <row r="4201">
+      <c r="A4201" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4201" s="1">
+        <v>0.070000000000000007</v>
+      </c>
+      <c r="C4201" s="1">
+        <v>0.02977940421833436</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>